--- a/data_dev/出庫.xlsx
+++ b/data_dev/出庫.xlsx
@@ -436,42 +436,42 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>貨號</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>規格</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>數量</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>出庫數量</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>單價</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>金額</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>日期</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>出庫日期</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>平台</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>貨號</t>
         </is>
       </c>
     </row>
@@ -483,36 +483,36 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>HGI03023-GY</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>M型短頸膚感防滑衣架</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>奶霧灰</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>1</v>
-      </c>
-      <c r="E2" t="n">
-        <v>135</v>
       </c>
       <c r="F2" t="n">
         <v>135</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" t="n">
+        <v>135</v>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>2026-02-01</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>蝦皮</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>HGI03023-GY</t>
         </is>
       </c>
     </row>
@@ -524,36 +524,36 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>HGI03023-BK</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>M型短頸膚感防滑衣架</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>黑色</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>75</v>
       </c>
       <c r="F3" t="n">
         <v>75</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" t="n">
+        <v>75</v>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>2026-02-01</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>蝦皮</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>HGI03023-BK</t>
         </is>
       </c>
     </row>
@@ -565,36 +565,36 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>HGI03024-40L</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>天山棉麻衣物整理摺疊收納箱</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>中號40L</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>2</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>75</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>150</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>2026-02-02</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>官網</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>HGI03024-40L</t>
         </is>
       </c>
     </row>
@@ -606,36 +606,36 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>HFA01019-BG-XL</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>厚磅撞色圓領短版修身短袖T恤</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>杏色XL</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>2</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>75</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>150</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>2026-02-02</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>官網</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>HFA01019-BG-XL</t>
         </is>
       </c>
     </row>
@@ -647,36 +647,36 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>HFA01019-DN-XL</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>厚磅撞色圓領短版修身短袖T恤</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>深藍XL</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>2</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>75</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>150</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>2026-02-02</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>官網</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>HFA01019-DN-XL</t>
         </is>
       </c>
     </row>
@@ -688,36 +688,36 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>HFA01019-DN-XL</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>厚磅撞色圓領短版修身短袖T恤</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>深藍XL</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>10</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>72</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>720</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>2026-02-02</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>官網</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>HFA01019-DN-XL</t>
         </is>
       </c>
     </row>
@@ -729,118 +729,118 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>HFA01019-BG-XL</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>厚磅撞色圓領短版修身短袖T恤</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>杏色M</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>3</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>杏色XL</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>195</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
+        <v>155</v>
+      </c>
+      <c r="G8" t="n">
+        <v>155</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>官網</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>HFA01019-BG-M</t>
+          <t>露天</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HGI03023</t>
+          <t>HFA01019</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M型短頸膚感防滑衣架</t>
+          <t>HFA01019-BG-M</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>燕麥白</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>2</v>
+          <t>厚磅撞色圓領短版修身短袖T恤</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>杏色M</t>
+        </is>
       </c>
       <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
         <v>65</v>
       </c>
-      <c r="F9" t="n">
-        <v>130</v>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" t="n">
+        <v>195</v>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>2026-02-04</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>官網</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>HGI03023-WH</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HFA01019</t>
+          <t>HGI03023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>厚磅撞色圓領短版修身短袖T恤</t>
+          <t>HGI03023-WH</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>深藍XL</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>5</v>
+          <t>M型短頸膚感防滑衣架</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>燕麥白</t>
+        </is>
       </c>
       <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
         <v>65</v>
       </c>
-      <c r="F10" t="n">
-        <v>325</v>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" t="n">
+        <v>130</v>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>2026-02-04</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>官網</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>HFA01019-DN-XL</t>
         </is>
       </c>
     </row>
@@ -852,118 +852,118 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>HFA01019-DN-XL</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>厚磅撞色圓領短版修身短袖T恤</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>深藍M</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>4</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>深藍XL</t>
+        </is>
       </c>
       <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
         <v>65</v>
       </c>
-      <c r="F11" t="n">
-        <v>260</v>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" t="n">
+        <v>325</v>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>2026-02-04</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>官網</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>HFA01019-DN-M</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HGI03023</t>
+          <t>HFA01019</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>M型短頸膚感防滑衣架</t>
+          <t>HFA01019-DN-M</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>黑色</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>3</v>
+          <t>厚磅撞色圓領短版修身短袖T恤</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>深藍M</t>
+        </is>
       </c>
       <c r="E12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" t="n">
         <v>65</v>
       </c>
-      <c r="F12" t="n">
-        <v>195</v>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" t="n">
+        <v>260</v>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>2026-02-04</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>官網</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>HGI03023-BK</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HFA01019</t>
+          <t>HGI03023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>厚磅撞色圓領短版修身短袖T恤</t>
+          <t>HGI03023-BK</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>深藍M</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
+          <t>M型短頸膚感防滑衣架</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
       </c>
       <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
         <v>65</v>
       </c>
-      <c r="F13" t="n">
-        <v>650</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="G13" t="n">
+        <v>195</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>官網</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>HFA01019-DN-M</t>
         </is>
       </c>
     </row>
@@ -975,36 +975,36 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>HFA01019-DN-M</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>厚磅撞色圓領短版修身短袖T恤</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>杏色M</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>深藍M</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
         <v>10</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>65</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>650</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>官網</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>HFA01019-BG-M</t>
         </is>
       </c>
     </row>
@@ -1016,36 +1016,36 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>HFA01019-BG-M</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>厚磅撞色圓領短版修身短袖T恤</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>杏色XL</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>1</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>杏色M</t>
+        </is>
       </c>
       <c r="E15" t="n">
-        <v>155</v>
+        <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>155</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2026/02/03</t>
-        </is>
+        <v>65</v>
+      </c>
+      <c r="G15" t="n">
+        <v>650</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>露天</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>HFA01019-BG-XL</t>
+          <t>官網</t>
         </is>
       </c>
     </row>
@@ -1057,36 +1057,36 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>HFA01019-DN-XL</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>厚磅撞色圓領短版修身短袖T恤</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>深藍XL</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>3</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>67</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>201</v>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2026/02/07</t>
-        </is>
-      </c>
       <c r="H16" t="inlineStr">
         <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>露天</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>HFA01019-DN-XL</t>
         </is>
       </c>
     </row>
@@ -1098,36 +1098,36 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>HFA01019-DN-M</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>厚磅撞色圓領短版修身短袖T恤</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>深藍M</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>1</v>
-      </c>
-      <c r="E17" t="n">
-        <v>67</v>
       </c>
       <c r="F17" t="n">
         <v>67</v>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2026/02/09</t>
-        </is>
+      <c r="G17" t="n">
+        <v>67</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>露天</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>HFA01019-DN-M</t>
         </is>
       </c>
     </row>
